--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5341,0.2545,0.3535,0.0411</t>
-  </si>
-  <si>
-    <t>0.7982,0.0417,0.0961,0.0848</t>
-  </si>
-  <si>
-    <t>0.5565,0.1418,0.2397,0.1960</t>
-  </si>
-  <si>
-    <t>0.5386,0.2570,0.2014,0.1271</t>
-  </si>
-  <si>
-    <t>0.4724,0.3280,0.3385,0.0697</t>
-  </si>
-  <si>
-    <t>0.2205,0.5938,0.4693,0.0194</t>
-  </si>
-  <si>
-    <t>0.5176,0.2671,0.2506,0.1405</t>
-  </si>
-  <si>
-    <t>0.5575,0.3019,0.2735,0.0642</t>
-  </si>
-  <si>
-    <t>0.4725,0.3138,0.3362,0.0762</t>
-  </si>
-  <si>
-    <t>0.3665,0.4679,0.4091,0.0308</t>
-  </si>
-  <si>
-    <t>0.4433,0.3698,0.3204,0.0838</t>
-  </si>
-  <si>
-    <t>0.3603,0.4617,0.3616,0.0596</t>
-  </si>
-  <si>
-    <t>0.6944,0.0886,0.2099,0.0694</t>
-  </si>
-  <si>
-    <t>0.5029,0.1756,0.3907,0.0835</t>
-  </si>
-  <si>
-    <t>0.4110,0.2745,0.4559,0.0463</t>
-  </si>
-  <si>
-    <t>0.3298,0.2391,0.5528,0.0320</t>
-  </si>
-  <si>
-    <t>0.5086,0.2374,0.3167,0.1064</t>
-  </si>
-  <si>
-    <t>0.1831,0.6802,0.4068,0.0229</t>
-  </si>
-  <si>
-    <t>0.3249,0.5708,0.3454,0.0357</t>
-  </si>
-  <si>
-    <t>0.2783,0.5190,0.4464,0.0590</t>
-  </si>
-  <si>
-    <t>0.1531,0.7659,0.3658,0.0207</t>
-  </si>
-  <si>
-    <t>0.1705,0.7577,0.3678,0.0236</t>
-  </si>
-  <si>
-    <t>0.7556,0.0686,0.1156,0.0992</t>
-  </si>
-  <si>
-    <t>0.7350,0.0492,0.2027,0.0601</t>
-  </si>
-  <si>
-    <t>0.4810,0.2064,0.4153,0.0289</t>
-  </si>
-  <si>
-    <t>0.6267,0.1103,0.3061,0.0497</t>
-  </si>
-  <si>
-    <t>0.3891,0.1938,0.5474,0.0477</t>
-  </si>
-  <si>
-    <t>0.5471,0.1319,0.3599,0.0684</t>
-  </si>
-  <si>
-    <t>0.5067,0.0676,0.5301,0.0112</t>
-  </si>
-  <si>
-    <t>0.3129,0.5645,0.3478,0.0334</t>
-  </si>
-  <si>
-    <t>0.3582,0.3580,0.3979,0.0766</t>
-  </si>
-  <si>
-    <t>0.0401,0.5607,0.8634,0.0077</t>
-  </si>
-  <si>
-    <t>0.4644,0.3712,0.2962,0.0252</t>
-  </si>
-  <si>
-    <t>0.7263,0.1210,0.1153,0.0902</t>
-  </si>
-  <si>
-    <t>0.3756,0.4379,0.3709,0.0627</t>
-  </si>
-  <si>
-    <t>0.2145,0.6736,0.3529,0.0587</t>
-  </si>
-  <si>
-    <t>0.2475,0.5441,0.4612,0.0580</t>
-  </si>
-  <si>
-    <t>0.1587,0.6702,0.2603,0.0340</t>
-  </si>
-  <si>
-    <t>0.5677,0.1454,0.2910,0.0521</t>
-  </si>
-  <si>
-    <t>0.4028,0.1927,0.5006,0.0332</t>
-  </si>
-  <si>
-    <t>0.5593,0.0918,0.3979,0.0470</t>
-  </si>
-  <si>
-    <t>0.2921,0.3728,0.4868,0.0494</t>
-  </si>
-  <si>
-    <t>0.3300,0.7008,0.0883,0.0097</t>
-  </si>
-  <si>
-    <t>0.2645,0.2554,0.6334,0.0306</t>
-  </si>
-  <si>
-    <t>0.6857,0.1150,0.1633,0.0957</t>
-  </si>
-  <si>
-    <t>0.2267,0.6555,0.3744,0.0574</t>
-  </si>
-  <si>
-    <t>0.3062,0.5172,0.3531,0.0477</t>
-  </si>
-  <si>
-    <t>0.3384,0.5252,0.3399,0.0475</t>
-  </si>
-  <si>
-    <t>0.1298,0.3919,0.6651,0.0210</t>
-  </si>
-  <si>
-    <t>0.1264,0.3658,0.7500,0.0154</t>
-  </si>
-  <si>
-    <t>0.3535,0.0962,0.6191,0.0355</t>
-  </si>
-  <si>
-    <t>0.7020,0.0789,0.2321,0.0510</t>
-  </si>
-  <si>
-    <t>0.1998,0.1856,0.7731,0.0104</t>
-  </si>
-  <si>
-    <t>0.1575,0.2508,0.7078,0.0094</t>
-  </si>
-  <si>
-    <t>0.3482,0.4601,0.3799,0.0489</t>
-  </si>
-  <si>
-    <t>0.5008,0.3466,0.3048,0.0677</t>
-  </si>
-  <si>
-    <t>0.4942,0.3936,0.2706,0.0579</t>
-  </si>
-  <si>
-    <t>0.1960,0.5388,0.6040,0.0400</t>
-  </si>
-  <si>
-    <t>0.4666,0.3283,0.3069,0.1231</t>
-  </si>
-  <si>
-    <t>0.3660,0.4607,0.3354,0.0644</t>
-  </si>
-  <si>
-    <t>0.4033,0.4334,0.3495,0.0596</t>
-  </si>
-  <si>
-    <t>0.0292,0.9377,0.2168,0.0013</t>
-  </si>
-  <si>
-    <t>0.2435,0.4541,0.4272,0.0598</t>
-  </si>
-  <si>
-    <t>0.2232,0.5443,0.3263,0.0086</t>
-  </si>
-  <si>
-    <t>0.0451,0.8619,0.3491,0.0048</t>
-  </si>
-  <si>
-    <t>0.1767,0.2588,0.7298,0.0302</t>
-  </si>
-  <si>
-    <t>0.4557,0.2871,0.3374,0.0724</t>
-  </si>
-  <si>
-    <t>0.1647,0.8351,0.1847,0.0111</t>
-  </si>
-  <si>
-    <t>0.5249,0.2364,0.2820,0.1393</t>
-  </si>
-  <si>
-    <t>0.3585,0.3679,0.4306,0.0917</t>
-  </si>
-  <si>
-    <t>0.0090,0.7600,0.8879,0.0018</t>
-  </si>
-  <si>
-    <t>0.0162,0.8875,0.7239,0.0028</t>
-  </si>
-  <si>
-    <t>0.2412,0.5949,0.3247,0.0154</t>
-  </si>
-  <si>
-    <t>0.1299,0.8337,0.1314,0.0073</t>
-  </si>
-  <si>
-    <t>0.0401,0.9318,0.2037,0.0065</t>
-  </si>
-  <si>
-    <t>0.6201,0.0710,0.2993,0.0980</t>
-  </si>
-  <si>
-    <t>0.6974,0.0755,0.0885,0.1901</t>
-  </si>
-  <si>
-    <t>0.7172,0.0901,0.0789,0.1665</t>
-  </si>
-  <si>
-    <t>0.6154,0.1114,0.2370,0.1567</t>
-  </si>
-  <si>
-    <t>0.6855,0.0959,0.1272,0.1769</t>
-  </si>
-  <si>
-    <t>0.6915,0.1745,0.1339,0.0668</t>
-  </si>
-  <si>
-    <t>0.0424,0.8655,0.4477,0.0078</t>
-  </si>
-  <si>
-    <t>0.1220,0.7382,0.3366,0.0092</t>
-  </si>
-  <si>
-    <t>0.2912,0.4066,0.4394,0.0214</t>
-  </si>
-  <si>
-    <t>0.1343,0.4835,0.6527,0.0211</t>
-  </si>
-  <si>
-    <t>0.1057,0.6669,0.4879,0.0086</t>
-  </si>
-  <si>
-    <t>0.0427,0.8191,0.6057,0.0052</t>
-  </si>
-  <si>
-    <t>0.4293,0.3708,0.3607,0.0794</t>
-  </si>
-  <si>
-    <t>0.3333,0.5155,0.3857,0.0583</t>
-  </si>
-  <si>
-    <t>0.3030,0.4021,0.5140,0.0625</t>
-  </si>
-  <si>
-    <t>0.5052,0.3278,0.2917,0.0918</t>
-  </si>
-  <si>
-    <t>0.4273,0.3679,0.3628,0.0709</t>
-  </si>
-  <si>
-    <t>0.5787,0.3170,0.1868,0.0660</t>
-  </si>
-  <si>
-    <t>0.3844,0.4467,0.3881,0.0717</t>
-  </si>
-  <si>
-    <t>0.2331,0.5453,0.4821,0.0465</t>
-  </si>
-  <si>
-    <t>0.3544,0.4443,0.4217,0.0584</t>
-  </si>
-  <si>
-    <t>0.4229,0.4404,0.3279,0.0702</t>
-  </si>
-  <si>
-    <t>0.4489,0.4026,0.3000,0.0733</t>
-  </si>
-  <si>
-    <t>0.5179,0.2823,0.2937,0.0991</t>
-  </si>
-  <si>
-    <t>0.3642,0.4249,0.4122,0.0511</t>
-  </si>
-  <si>
-    <t>0.3440,0.4858,0.3824,0.0708</t>
-  </si>
-  <si>
-    <t>0.4522,0.3357,0.3358,0.1067</t>
-  </si>
-  <si>
-    <t>0.5026,0.2537,0.3097,0.1257</t>
-  </si>
-  <si>
-    <t>0.3345,0.0705,0.7262,0.0133</t>
-  </si>
-  <si>
-    <t>0.2358,0.2369,0.6609,0.0263</t>
-  </si>
-  <si>
-    <t>0.5146,0.0919,0.3538,0.1172</t>
-  </si>
-  <si>
-    <t>0.4820,0.1289,0.4530,0.0576</t>
-  </si>
-  <si>
-    <t>0.3004,0.4201,0.4633,0.0718</t>
-  </si>
-  <si>
-    <t>0.0760,0.8137,0.5120,0.0147</t>
-  </si>
-  <si>
-    <t>0.1866,0.7226,0.3646,0.0279</t>
-  </si>
-  <si>
-    <t>0.3298,0.5837,0.3132,0.0406</t>
-  </si>
-  <si>
-    <t>0.1306,0.7975,0.3510,0.0144</t>
-  </si>
-  <si>
-    <t>0.0846,0.8556,0.3600,0.0139</t>
-  </si>
-  <si>
-    <t>0.3347,0.5639,0.3151,0.0665</t>
-  </si>
-  <si>
-    <t>0.7316,0.1256,0.1356,0.0588</t>
-  </si>
-  <si>
-    <t>0.6381,0.1434,0.2519,0.0652</t>
-  </si>
-  <si>
-    <t>0.6153,0.1082,0.2230,0.1641</t>
-  </si>
-  <si>
-    <t>0.7232,0.1082,0.2087,0.0403</t>
-  </si>
-  <si>
-    <t>0.4270,0.2094,0.3903,0.1682</t>
-  </si>
-  <si>
-    <t>0.2492,0.5353,0.4479,0.0460</t>
-  </si>
-  <si>
-    <t>0.2322,0.6910,0.2832,0.0321</t>
-  </si>
-  <si>
-    <t>0.4841,0.2048,0.3106,0.1354</t>
-  </si>
-  <si>
-    <t>0.1456,0.7518,0.2608,0.0081</t>
-  </si>
-  <si>
-    <t>0.3971,0.3786,0.3751,0.0736</t>
-  </si>
-  <si>
-    <t>0.3089,0.4900,0.4264,0.0462</t>
-  </si>
-  <si>
-    <t>0.3543,0.4508,0.4015,0.0525</t>
-  </si>
-  <si>
-    <t>0.3596,0.4549,0.3759,0.0583</t>
-  </si>
-  <si>
-    <t>0.4991,0.3052,0.3158,0.0970</t>
-  </si>
-  <si>
-    <t>0.5549,0.2284,0.2575,0.1000</t>
-  </si>
-  <si>
-    <t>0.4380,0.3187,0.3693,0.0905</t>
-  </si>
-  <si>
-    <t>0.3899,0.4581,0.3343,0.0450</t>
-  </si>
-  <si>
-    <t>0.4925,0.3940,0.2508,0.0383</t>
-  </si>
-  <si>
-    <t>0.5295,0.2182,0.3336,0.1169</t>
-  </si>
-  <si>
-    <t>0.4425,0.4061,0.3235,0.0745</t>
-  </si>
-  <si>
-    <t>0.1097,0.4792,0.6384,0.0056</t>
-  </si>
-  <si>
-    <t>0.5508,0.3708,0.1376,0.0134</t>
-  </si>
-  <si>
-    <t>0.3972,0.4406,0.2607,0.0245</t>
-  </si>
-  <si>
-    <t>0.3559,0.3602,0.3952,0.0401</t>
-  </si>
-  <si>
-    <t>0.6819,0.0978,0.2228,0.0742</t>
-  </si>
-  <si>
-    <t>0.3326,0.2239,0.5172,0.0965</t>
-  </si>
-  <si>
-    <t>0.7503,0.0542,0.1672,0.0699</t>
-  </si>
-  <si>
-    <t>0.6637,0.1051,0.1885,0.1341</t>
-  </si>
-  <si>
-    <t>0.4728,0.2351,0.2617,0.2030</t>
-  </si>
-  <si>
-    <t>0.6885,0.0516,0.0762,0.2642</t>
-  </si>
-  <si>
-    <t>0.7516,0.0758,0.1044,0.1349</t>
-  </si>
-  <si>
-    <t>0.6813,0.1093,0.1804,0.0899</t>
-  </si>
-  <si>
-    <t>0.1147,0.7956,0.2924,0.0134</t>
-  </si>
-  <si>
-    <t>0.4264,0.3875,0.3449,0.0782</t>
-  </si>
-  <si>
-    <t>0.4198,0.3610,0.3630,0.0740</t>
-  </si>
-  <si>
-    <t>0.5206,0.2960,0.3097,0.0595</t>
-  </si>
-  <si>
-    <t>0.3799,0.4919,0.3510,0.0527</t>
-  </si>
-  <si>
-    <t>0.4785,0.2953,0.3332,0.0472</t>
-  </si>
-  <si>
-    <t>0.8291,0.0498,0.0789,0.0584</t>
-  </si>
-  <si>
-    <t>0.6085,0.1425,0.3153,0.0727</t>
-  </si>
-  <si>
-    <t>0.0678,0.6561,0.7577,0.0204</t>
-  </si>
-  <si>
-    <t>0.7622,0.0736,0.0598,0.1060</t>
-  </si>
-  <si>
-    <t>0.6191,0.1676,0.2456,0.1236</t>
-  </si>
-  <si>
-    <t>0.3759,0.4101,0.3803,0.0818</t>
-  </si>
-  <si>
-    <t>0.5085,0.2317,0.3071,0.1048</t>
-  </si>
-  <si>
-    <t>0.5426,0.2107,0.2923,0.1626</t>
-  </si>
-  <si>
-    <t>0.4432,0.2782,0.3497,0.1030</t>
-  </si>
-  <si>
-    <t>0.4869,0.2989,0.3063,0.0966</t>
-  </si>
-  <si>
-    <t>0.4660,0.3086,0.3403,0.0799</t>
-  </si>
-  <si>
-    <t>0.1919,0.6171,0.5121,0.0378</t>
-  </si>
-  <si>
-    <t>0.4230,0.3792,0.3535,0.0859</t>
-  </si>
-  <si>
-    <t>0.4418,0.3656,0.3457,0.0914</t>
-  </si>
-  <si>
-    <t>0.5761,0.2457,0.2834,0.0532</t>
-  </si>
-  <si>
-    <t>0.6224,0.2108,0.1779,0.1134</t>
-  </si>
-  <si>
-    <t>0.4068,0.3602,0.3830,0.0725</t>
-  </si>
-  <si>
-    <t>0.3071,0.4882,0.4464,0.0689</t>
-  </si>
-  <si>
-    <t>0.5643,0.2402,0.2869,0.0722</t>
-  </si>
-  <si>
-    <t>0.3190,0.4976,0.3553,0.0547</t>
-  </si>
-  <si>
-    <t>0.2422,0.6130,0.4430,0.0443</t>
-  </si>
-  <si>
-    <t>0.2562,0.6408,0.3532,0.0306</t>
-  </si>
-  <si>
-    <t>0.4411,0.2325,0.2929,0.2082</t>
-  </si>
-  <si>
-    <t>0.3681,0.4749,0.3406,0.0825</t>
-  </si>
-  <si>
-    <t>0.3134,0.4521,0.4189,0.0892</t>
-  </si>
-  <si>
-    <t>0.3792,0.5160,0.3328,0.0613</t>
-  </si>
-  <si>
-    <t>0.3833,0.3824,0.4140,0.0863</t>
-  </si>
-  <si>
-    <t>0.0102,0.5203,0.9499,0.0014</t>
-  </si>
-  <si>
-    <t>0.2017,0.6518,0.4189,0.0317</t>
-  </si>
-  <si>
-    <t>0.1212,0.1794,0.8266,0.0048</t>
-  </si>
-  <si>
-    <t>0.0756,0.4594,0.7957,0.0133</t>
-  </si>
-  <si>
-    <t>0.2537,0.3519,0.5587,0.0239</t>
-  </si>
-  <si>
-    <t>0.3494,0.5453,0.2221,0.0251</t>
-  </si>
-  <si>
-    <t>0.3648,0.1014,0.6032,0.0177</t>
-  </si>
-  <si>
-    <t>0.5139,0.1058,0.4880,0.0185</t>
-  </si>
-  <si>
-    <t>0.3047,0.2369,0.5455,0.0322</t>
-  </si>
-  <si>
-    <t>0.6389,0.1863,0.2098,0.0897</t>
-  </si>
-  <si>
-    <t>0.5268,0.2632,0.2782,0.0795</t>
-  </si>
-  <si>
-    <t>0.5585,0.1110,0.2975,0.1398</t>
-  </si>
-  <si>
-    <t>0.4499,0.3595,0.3191,0.0670</t>
-  </si>
-  <si>
-    <t>0.5147,0.3200,0.2618,0.0404</t>
-  </si>
-  <si>
-    <t>0.7189,0.1061,0.1800,0.0403</t>
-  </si>
-  <si>
-    <t>0.6309,0.1454,0.2195,0.1416</t>
-  </si>
-  <si>
-    <t>0.5956,0.1233,0.3216,0.0764</t>
-  </si>
-  <si>
-    <t>0.3806,0.4469,0.3288,0.0621</t>
-  </si>
-  <si>
-    <t>0.4210,0.3227,0.3895,0.0934</t>
-  </si>
-  <si>
-    <t>0.3506,0.5131,0.2961,0.0550</t>
-  </si>
-  <si>
-    <t>0.2881,0.5187,0.4128,0.0478</t>
-  </si>
-  <si>
-    <t>0.3292,0.5351,0.3093,0.0499</t>
-  </si>
-  <si>
-    <t>0.5995,0.1443,0.1937,0.1862</t>
-  </si>
-  <si>
-    <t>0.6886,0.1506,0.1587,0.0534</t>
-  </si>
-  <si>
-    <t>0.6821,0.1805,0.1602,0.0527</t>
-  </si>
-  <si>
-    <t>0.7459,0.0902,0.1459,0.0465</t>
-  </si>
-  <si>
-    <t>0.5449,0.1646,0.3376,0.0662</t>
-  </si>
-  <si>
-    <t>0.1808,0.3336,0.6804,0.0139</t>
-  </si>
-  <si>
-    <t>0.1232,0.6804,0.5079,0.0456</t>
-  </si>
-  <si>
-    <t>0.3804,0.2331,0.5097,0.0468</t>
-  </si>
-  <si>
-    <t>0.3062,0.3916,0.4211,0.0350</t>
-  </si>
-  <si>
-    <t>0.3528,0.2969,0.4557,0.0411</t>
-  </si>
-  <si>
-    <t>0.6113,0.1881,0.2078,0.1494</t>
-  </si>
-  <si>
-    <t>0.2093,0.5928,0.5161,0.0340</t>
-  </si>
-  <si>
-    <t>0.5405,0.3171,0.2654,0.0762</t>
-  </si>
-  <si>
-    <t>0.3704,0.4519,0.3869,0.0382</t>
-  </si>
-  <si>
-    <t>0.3115,0.4372,0.4580,0.0694</t>
-  </si>
-  <si>
-    <t>0.3513,0.4958,0.3833,0.0604</t>
-  </si>
-  <si>
-    <t>0.3735,0.5172,0.3165,0.0370</t>
-  </si>
-  <si>
-    <t>0.4640,0.3618,0.3184,0.0413</t>
-  </si>
-  <si>
-    <t>0.6025,0.1479,0.2638,0.1025</t>
-  </si>
-  <si>
-    <t>0.6245,0.1494,0.2377,0.1135</t>
-  </si>
-  <si>
-    <t>0.2385,0.5186,0.4616,0.0609</t>
-  </si>
-  <si>
-    <t>0.1705,0.2568,0.7132,0.0138</t>
-  </si>
-  <si>
-    <t>0.2883,0.6050,0.1814,0.0169</t>
-  </si>
-  <si>
-    <t>0.5434,0.1470,0.4111,0.0312</t>
-  </si>
-  <si>
-    <t>0.1104,0.3613,0.7304,0.0073</t>
-  </si>
-  <si>
-    <t>0.1756,0.3287,0.7013,0.0221</t>
-  </si>
-  <si>
-    <t>0.2009,0.4182,0.4555,0.0369</t>
-  </si>
-  <si>
-    <t>0.3236,0.1980,0.5487,0.0337</t>
-  </si>
-  <si>
-    <t>0.4573,0.2461,0.3959,0.0827</t>
-  </si>
-  <si>
-    <t>0.6822,0.0946,0.2618,0.0527</t>
-  </si>
-  <si>
-    <t>0.5412,0.1358,0.3519,0.0940</t>
-  </si>
-  <si>
-    <t>0.5144,0.2558,0.3231,0.1143</t>
-  </si>
-  <si>
-    <t>0.5405,0.2503,0.2935,0.1002</t>
-  </si>
-  <si>
-    <t>0.3288,0.4854,0.4482,0.0416</t>
-  </si>
-  <si>
-    <t>0.5747,0.2766,0.2351,0.0711</t>
-  </si>
-  <si>
-    <t>0.4755,0.4209,0.3185,0.0428</t>
-  </si>
-  <si>
-    <t>0.6215,0.2352,0.2449,0.0741</t>
-  </si>
-  <si>
-    <t>0.4934,0.2602,0.3075,0.1015</t>
-  </si>
-  <si>
-    <t>0.3035,0.5161,0.4077,0.0553</t>
-  </si>
-  <si>
-    <t>0.4292,0.3349,0.3490,0.1374</t>
-  </si>
-  <si>
-    <t>0.3907,0.1826,0.5433,0.0357</t>
-  </si>
-  <si>
-    <t>0.0203,0.7641,0.7438,0.0019</t>
-  </si>
-  <si>
-    <t>0.2078,0.4346,0.4868,0.0109</t>
-  </si>
-  <si>
-    <t>0.4458,0.3096,0.3565,0.0874</t>
-  </si>
-  <si>
-    <t>0.2580,0.1935,0.6588,0.0226</t>
-  </si>
-  <si>
-    <t>0.5215,0.1783,0.3789,0.0956</t>
-  </si>
-  <si>
-    <t>0.4521,0.1442,0.3100,0.2307</t>
-  </si>
-  <si>
-    <t>0.5419,0.0971,0.3697,0.0529</t>
-  </si>
-  <si>
-    <t>0.5832,0.1790,0.2426,0.1339</t>
-  </si>
-  <si>
-    <t>0.5670,0.0688,0.1750,0.2921</t>
-  </si>
-  <si>
-    <t>0.7224,0.0940,0.1043,0.1474</t>
-  </si>
-  <si>
-    <t>0.5136,0.1375,0.2071,0.2806</t>
-  </si>
-  <si>
-    <t>0.7294,0.0723,0.0732,0.1852</t>
-  </si>
-  <si>
-    <t>0.5448,0.2800,0.2465,0.0474</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.7897,0.0236,0.0518,0.1244</t>
+  </si>
+  <si>
+    <t>0.0016,0.0010,0.0007,0.9985</t>
+  </si>
+  <si>
+    <t>0.7396,0.0020,0.0082,0.3011</t>
+  </si>
+  <si>
+    <t>0.0077,0.0131,0.0028,0.9927</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9913,0.0018,0.0011,0.0031</t>
+  </si>
+  <si>
+    <t>0.9966,0.0007,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9941,0.0023,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9926,0.0027,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.9944,0.0014,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.8100,0.0108,0.2010,0.0197</t>
+  </si>
+  <si>
+    <t>0.1106,0.1054,0.7646,0.0346</t>
+  </si>
+  <si>
+    <t>0.1729,0.0191,0.8727,0.0022</t>
+  </si>
+  <si>
+    <t>0.0436,0.0173,0.9348,0.0049</t>
+  </si>
+  <si>
+    <t>0.4589,0.0098,0.6828,0.0118</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0083,0.9830,0.0096,0.0005</t>
+  </si>
+  <si>
+    <t>0.0731,0.9237,0.0121,0.0028</t>
+  </si>
+  <si>
+    <t>0.0045,0.9904,0.0063,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.9984,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.6009,0.0103,0.5077,0.0127</t>
+  </si>
+  <si>
+    <t>0.3265,0.0064,0.7200,0.0170</t>
+  </si>
+  <si>
+    <t>0.0135,0.0023,0.9879,0.0014</t>
+  </si>
+  <si>
+    <t>0.1038,0.1252,0.7148,0.0586</t>
+  </si>
+  <si>
+    <t>0.0372,0.0102,0.9558,0.0055</t>
+  </si>
+  <si>
+    <t>0.1192,0.0366,0.8460,0.0181</t>
+  </si>
+  <si>
+    <t>0.0027,0.0047,0.9846,0.0181</t>
+  </si>
+  <si>
+    <t>0.6594,0.3853,0.0212,0.0043</t>
+  </si>
+  <si>
+    <t>0.5260,0.0815,0.4600,0.0129</t>
+  </si>
+  <si>
+    <t>0.0002,0.0136,0.9982,0.0019</t>
+  </si>
+  <si>
+    <t>0.0065,0.9693,0.0344,0.0005</t>
+  </si>
+  <si>
+    <t>0.8909,0.0447,0.0278,0.0400</t>
+  </si>
+  <si>
+    <t>0.1789,0.0411,0.7808,0.0453</t>
+  </si>
+  <si>
+    <t>0.8646,0.1989,0.0081,0.0020</t>
+  </si>
+  <si>
+    <t>0.0279,0.9248,0.2445,0.0015</t>
+  </si>
+  <si>
+    <t>0.0184,0.8982,0.2590,0.0067</t>
+  </si>
+  <si>
+    <t>0.0280,0.0344,0.9406,0.0171</t>
+  </si>
+  <si>
+    <t>0.0682,0.0579,0.8885,0.0226</t>
+  </si>
+  <si>
+    <t>0.2150,0.0169,0.7741,0.0260</t>
+  </si>
+  <si>
+    <t>0.0306,0.1216,0.8970,0.0124</t>
+  </si>
+  <si>
+    <t>0.0106,0.9765,0.0229,0.0014</t>
+  </si>
+  <si>
+    <t>0.0056,0.0171,0.9727,0.0184</t>
+  </si>
+  <si>
+    <t>0.0439,0.1537,0.0065,0.9364</t>
+  </si>
+  <si>
+    <t>0.0037,0.9885,0.0080,0.0117</t>
+  </si>
+  <si>
+    <t>0.0025,0.9864,0.0604,0.0012</t>
+  </si>
+  <si>
+    <t>0.0019,0.9910,0.0262,0.0029</t>
+  </si>
+  <si>
+    <t>0.0018,0.0308,0.9863,0.0065</t>
+  </si>
+  <si>
+    <t>0.0074,0.7127,0.7861,0.0011</t>
+  </si>
+  <si>
+    <t>0.0395,0.0213,0.8998,0.0203</t>
+  </si>
+  <si>
+    <t>0.0021,0.0077,0.9875,0.0133</t>
+  </si>
+  <si>
+    <t>0.0016,0.0107,0.9897,0.0098</t>
+  </si>
+  <si>
+    <t>0.0121,0.6174,0.8729,0.0036</t>
+  </si>
+  <si>
+    <t>0.9568,0.0396,0.0068,0.0031</t>
+  </si>
+  <si>
+    <t>0.9851,0.0041,0.0048,0.0033</t>
+  </si>
+  <si>
+    <t>0.9882,0.0020,0.0022,0.0047</t>
+  </si>
+  <si>
+    <t>0.0068,0.0294,0.9885,0.0033</t>
+  </si>
+  <si>
+    <t>0.9835,0.0060,0.0022,0.0039</t>
+  </si>
+  <si>
+    <t>0.9875,0.0081,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9764,0.0205,0.0060,0.0011</t>
+  </si>
+  <si>
+    <t>0.0018,0.8676,0.9251,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0542,0.9929,0.0027</t>
+  </si>
+  <si>
+    <t>0.0266,0.2135,0.8594,0.0293</t>
+  </si>
+  <si>
+    <t>0.0004,0.9663,0.9052,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0031,0.9990,0.0007</t>
+  </si>
+  <si>
+    <t>0.0190,0.9486,0.0319,0.0005</t>
+  </si>
+  <si>
+    <t>0.0122,0.9892,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9590,0.0045,0.0560,0.0039</t>
+  </si>
+  <si>
+    <t>0.2274,0.2277,0.6919,0.0334</t>
+  </si>
+  <si>
+    <t>0.0029,0.0153,0.9916,0.0038</t>
+  </si>
+  <si>
+    <t>0.0005,0.9829,0.7790,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.8254,0.8559,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.9944,0.1449,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.8912,0.8810,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.0018,0.9982</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0029,0.0012,0.0014,0.9975</t>
+  </si>
+  <si>
+    <t>0.0120,0.0025,0.0033,0.9913</t>
+  </si>
+  <si>
+    <t>0.0078,0.0010,0.0009,0.9957</t>
+  </si>
+  <si>
+    <t>0.0013,0.0013,0.0032,0.9974</t>
+  </si>
+  <si>
+    <t>0.0010,0.9791,0.6343,0.0005</t>
+  </si>
+  <si>
+    <t>0.0059,0.7268,0.8906,0.0014</t>
+  </si>
+  <si>
+    <t>0.0068,0.8989,0.6532,0.0026</t>
+  </si>
+  <si>
+    <t>0.0032,0.6408,0.9282,0.0029</t>
+  </si>
+  <si>
+    <t>0.0009,0.9665,0.6125,0.0002</t>
+  </si>
+  <si>
+    <t>0.0097,0.6764,0.8154,0.0020</t>
+  </si>
+  <si>
+    <t>0.9940,0.0020,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9650,0.0378,0.0058,0.0022</t>
+  </si>
+  <si>
+    <t>0.9802,0.0181,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9799,0.0055,0.0041,0.0076</t>
+  </si>
+  <si>
+    <t>0.9876,0.0042,0.0029,0.0027</t>
+  </si>
+  <si>
+    <t>0.9862,0.0030,0.0038,0.0044</t>
+  </si>
+  <si>
+    <t>0.9867,0.0054,0.0026,0.0024</t>
+  </si>
+  <si>
+    <t>0.9889,0.0075,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9943,0.0019,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9912,0.0019,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9920,0.0027,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9784,0.0059,0.0053,0.0082</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9910,0.0026,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.0008,0.0012,0.9945,0.0063</t>
+  </si>
+  <si>
+    <t>0.1514,0.0207,0.8682,0.0086</t>
+  </si>
+  <si>
+    <t>0.9511,0.0019,0.0365,0.0105</t>
+  </si>
+  <si>
+    <t>0.0865,0.0019,0.9016,0.0134</t>
+  </si>
+  <si>
+    <t>0.0085,0.9860,0.0048,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9944,0.0047,0.0005</t>
+  </si>
+  <si>
+    <t>0.0239,0.9731,0.0038,0.0025</t>
+  </si>
+  <si>
+    <t>0.1006,0.8477,0.0461,0.0061</t>
+  </si>
+  <si>
+    <t>0.0122,0.9779,0.0136,0.0008</t>
+  </si>
+  <si>
+    <t>0.0032,0.9915,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.6949,0.4679,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.1297,0.1339,0.8067,0.0269</t>
+  </si>
+  <si>
+    <t>0.3212,0.0134,0.7473,0.0079</t>
+  </si>
+  <si>
+    <t>0.7555,0.0226,0.1945,0.0508</t>
+  </si>
+  <si>
+    <t>0.1945,0.1802,0.5912,0.0119</t>
+  </si>
+  <si>
+    <t>0.0141,0.7097,0.0116,0.8948</t>
+  </si>
+  <si>
+    <t>0.0026,0.9889,0.0328,0.0034</t>
+  </si>
+  <si>
+    <t>0.0078,0.9795,0.0195,0.0061</t>
+  </si>
+  <si>
+    <t>0.0032,0.9789,0.0271,0.0374</t>
+  </si>
+  <si>
+    <t>0.0008,0.9776,0.7424,0.0003</t>
+  </si>
+  <si>
+    <t>0.0075,0.9766,0.0895,0.0002</t>
+  </si>
+  <si>
+    <t>0.9105,0.1423,0.0053,0.0014</t>
+  </si>
+  <si>
+    <t>0.9324,0.0819,0.0057,0.0030</t>
+  </si>
+  <si>
+    <t>0.9676,0.0222,0.0062,0.0032</t>
+  </si>
+  <si>
+    <t>0.9872,0.0028,0.0024,0.0051</t>
+  </si>
+  <si>
+    <t>0.9881,0.0016,0.0035,0.0042</t>
+  </si>
+  <si>
+    <t>0.9892,0.0009,0.0017,0.0066</t>
+  </si>
+  <si>
+    <t>0.9921,0.0031,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9818,0.0069,0.0055,0.0034</t>
+  </si>
+  <si>
+    <t>0.9933,0.0013,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9894,0.0019,0.0037,0.0022</t>
+  </si>
+  <si>
+    <t>0.0024,0.4424,0.9728,0.0009</t>
+  </si>
+  <si>
+    <t>0.0074,0.4559,0.9199,0.0011</t>
+  </si>
+  <si>
+    <t>0.0146,0.3111,0.8898,0.0020</t>
+  </si>
+  <si>
+    <t>0.0150,0.0467,0.9499,0.0015</t>
+  </si>
+  <si>
+    <t>0.8968,0.0021,0.0072,0.0968</t>
+  </si>
+  <si>
+    <t>0.9001,0.0031,0.0957,0.0147</t>
+  </si>
+  <si>
+    <t>0.1067,0.0044,0.9154,0.0092</t>
+  </si>
+  <si>
+    <t>0.8327,0.0199,0.1167,0.0398</t>
+  </si>
+  <si>
+    <t>0.0099,0.0006,0.0013,0.9943</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.0030,0.9991</t>
+  </si>
+  <si>
+    <t>0.0009,0.0029,0.0024,0.9980</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.0031,0.9980</t>
+  </si>
+  <si>
+    <t>0.0117,0.6999,0.8109,0.0090</t>
+  </si>
+  <si>
+    <t>0.9819,0.0046,0.0089,0.0026</t>
+  </si>
+  <si>
+    <t>0.1164,0.8752,0.0099,0.0169</t>
+  </si>
+  <si>
+    <t>0.9887,0.0023,0.0039,0.0033</t>
+  </si>
+  <si>
+    <t>0.6863,0.4268,0.0090,0.0055</t>
+  </si>
+  <si>
+    <t>0.8231,0.0031,0.0043,0.2635</t>
+  </si>
+  <si>
+    <t>0.0876,0.0022,0.0034,0.9655</t>
+  </si>
+  <si>
+    <t>0.9797,0.0008,0.0018,0.0187</t>
+  </si>
+  <si>
+    <t>0.0013,0.0570,0.9858,0.0132</t>
+  </si>
+  <si>
+    <t>0.8762,0.0029,0.0008,0.1942</t>
+  </si>
+  <si>
+    <t>0.8190,0.0025,0.0018,0.3260</t>
+  </si>
+  <si>
+    <t>0.7346,0.1894,0.0687,0.0445</t>
+  </si>
+  <si>
+    <t>0.8046,0.0079,0.0209,0.1890</t>
+  </si>
+  <si>
+    <t>0.9446,0.0117,0.0458,0.0046</t>
+  </si>
+  <si>
+    <t>0.6387,0.1488,0.1265,0.1021</t>
+  </si>
+  <si>
+    <t>0.7678,0.0929,0.1590,0.0257</t>
+  </si>
+  <si>
+    <t>0.7473,0.2573,0.0412,0.0085</t>
+  </si>
+  <si>
+    <t>0.9857,0.0020,0.0044,0.0054</t>
+  </si>
+  <si>
+    <t>0.9852,0.0012,0.0010,0.0134</t>
+  </si>
+  <si>
+    <t>0.9868,0.0032,0.0037,0.0045</t>
+  </si>
+  <si>
+    <t>0.9937,0.0006,0.0005,0.0040</t>
+  </si>
+  <si>
+    <t>0.9948,0.0006,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9644,0.0173,0.0103,0.0069</t>
+  </si>
+  <si>
+    <t>0.9937,0.0013,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9938,0.0010,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.7097,0.4046,0.0127,0.0036</t>
+  </si>
+  <si>
+    <t>0.4878,0.6043,0.0175,0.0068</t>
+  </si>
+  <si>
+    <t>0.6056,0.5094,0.0180,0.0041</t>
+  </si>
+  <si>
+    <t>0.4001,0.0838,0.6514,0.0077</t>
+  </si>
+  <si>
+    <t>0.9465,0.0503,0.0094,0.0042</t>
+  </si>
+  <si>
+    <t>0.8560,0.0799,0.0754,0.0070</t>
+  </si>
+  <si>
+    <t>0.9689,0.0198,0.0085,0.0032</t>
+  </si>
+  <si>
+    <t>0.9818,0.0089,0.0037,0.0027</t>
+  </si>
+  <si>
+    <t>0.0013,0.0359,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.9247,0.0313,0.0545,0.0100</t>
+  </si>
+  <si>
+    <t>0.0038,0.0149,0.9887,0.0050</t>
+  </si>
+  <si>
+    <t>0.0077,0.0321,0.9735,0.0112</t>
+  </si>
+  <si>
+    <t>0.0119,0.0107,0.9816,0.0051</t>
+  </si>
+  <si>
+    <t>0.0177,0.0670,0.9474,0.0066</t>
+  </si>
+  <si>
+    <t>0.0024,0.0369,0.9864,0.0044</t>
+  </si>
+  <si>
+    <t>0.0063,0.0102,0.9897,0.0016</t>
+  </si>
+  <si>
+    <t>0.0054,0.0117,0.9881,0.0035</t>
+  </si>
+  <si>
+    <t>0.1153,0.0245,0.8614,0.0224</t>
+  </si>
+  <si>
+    <t>0.0917,0.0346,0.8695,0.0151</t>
+  </si>
+  <si>
+    <t>0.3906,0.0683,0.6225,0.0203</t>
+  </si>
+  <si>
+    <t>0.1384,0.0360,0.8114,0.0156</t>
+  </si>
+  <si>
+    <t>0.2284,0.4049,0.3531,0.0446</t>
+  </si>
+  <si>
+    <t>0.1912,0.5461,0.1916,0.0274</t>
+  </si>
+  <si>
+    <t>0.6456,0.0201,0.0930,0.2248</t>
+  </si>
+  <si>
+    <t>0.1931,0.1258,0.7306,0.0189</t>
+  </si>
+  <si>
+    <t>0.2292,0.8061,0.0245,0.0063</t>
+  </si>
+  <si>
+    <t>0.4492,0.5775,0.0259,0.0037</t>
+  </si>
+  <si>
+    <t>0.4284,0.7030,0.0061,0.0044</t>
+  </si>
+  <si>
+    <t>0.8417,0.2516,0.0063,0.0024</t>
+  </si>
+  <si>
+    <t>0.1548,0.8899,0.0066,0.0031</t>
+  </si>
+  <si>
+    <t>0.7052,0.1390,0.1454,0.0297</t>
+  </si>
+  <si>
+    <t>0.9240,0.0048,0.0307,0.0282</t>
+  </si>
+  <si>
+    <t>0.4253,0.0030,0.0099,0.6543</t>
+  </si>
+  <si>
+    <t>0.7464,0.0146,0.2053,0.0523</t>
+  </si>
+  <si>
+    <t>0.2715,0.0084,0.2154,0.4010</t>
+  </si>
+  <si>
+    <t>0.0036,0.0039,0.9780,0.0202</t>
+  </si>
+  <si>
+    <t>0.0088,0.0330,0.9674,0.0074</t>
+  </si>
+  <si>
+    <t>0.0273,0.0450,0.9350,0.0127</t>
+  </si>
+  <si>
+    <t>0.1420,0.1182,0.7387,0.0353</t>
+  </si>
+  <si>
+    <t>0.0045,0.0204,0.9854,0.0027</t>
+  </si>
+  <si>
+    <t>0.9931,0.0026,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9908,0.0039,0.0024,0.0013</t>
+  </si>
+  <si>
+    <t>0.9901,0.0031,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9876,0.0037,0.0039,0.0022</t>
+  </si>
+  <si>
+    <t>0.9913,0.0042,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9920,0.0012,0.0017,0.0033</t>
+  </si>
+  <si>
+    <t>0.9802,0.0075,0.0033,0.0056</t>
+  </si>
+  <si>
+    <t>0.0421,0.0394,0.9293,0.0259</t>
+  </si>
+  <si>
+    <t>0.2073,0.4620,0.5599,0.0291</t>
+  </si>
+  <si>
+    <t>0.6845,0.0397,0.2168,0.1042</t>
+  </si>
+  <si>
+    <t>0.0009,0.0117,0.9936,0.0043</t>
+  </si>
+  <si>
+    <t>0.0008,0.0099,0.9938,0.0050</t>
+  </si>
+  <si>
+    <t>0.0147,0.0957,0.9432,0.0060</t>
+  </si>
+  <si>
+    <t>0.0006,0.0036,0.9963,0.0025</t>
+  </si>
+  <si>
+    <t>0.1267,0.0110,0.8928,0.0077</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9956,0.0058</t>
+  </si>
+  <si>
+    <t>0.0223,0.0490,0.9323,0.0150</t>
+  </si>
+  <si>
+    <t>0.0484,0.0422,0.8961,0.0118</t>
+  </si>
+  <si>
+    <t>0.5094,0.0232,0.1744,0.2887</t>
+  </si>
+  <si>
+    <t>0.1838,0.0100,0.8519,0.0103</t>
+  </si>
+  <si>
+    <t>0.5832,0.0041,0.0089,0.5121</t>
+  </si>
+  <si>
+    <t>0.9821,0.0104,0.0030,0.0023</t>
+  </si>
+  <si>
+    <t>0.9938,0.0018,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9861,0.0059,0.0036,0.0021</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9910,0.0046,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9856,0.0045,0.0051,0.0034</t>
+  </si>
+  <si>
+    <t>0.9873,0.0053,0.0019,0.0028</t>
+  </si>
+  <si>
+    <t>0.0408,0.1729,0.8311,0.0052</t>
+  </si>
+  <si>
+    <t>0.0012,0.0090,0.9955,0.0009</t>
+  </si>
+  <si>
+    <t>0.0043,0.0253,0.9832,0.0066</t>
+  </si>
+  <si>
+    <t>0.1098,0.1645,0.7081,0.0250</t>
+  </si>
+  <si>
+    <t>0.0098,0.0331,0.9751,0.0056</t>
+  </si>
+  <si>
+    <t>0.0605,0.0048,0.8013,0.1333</t>
+  </si>
+  <si>
+    <t>0.0358,0.0280,0.9290,0.0216</t>
+  </si>
+  <si>
+    <t>0.0207,0.0062,0.7110,0.3212</t>
+  </si>
+  <si>
+    <t>0.6942,0.0028,0.0105,0.3727</t>
+  </si>
+  <si>
+    <t>0.0061,0.0130,0.0032,0.9939</t>
+  </si>
+  <si>
+    <t>0.0039,0.0006,0.0012,0.9969</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.0013,0.9988</t>
+  </si>
+  <si>
+    <t>0.6900,0.0169,0.0081,0.3368</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,10 +2026,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,10 +3188,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,10 +3202,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,10 +3272,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,10 +4238,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,10 +4434,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4476,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,10 +4924,10 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,10 +4994,10 @@
         <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,10 +5134,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,10 +5302,10 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
